--- a/data/RouteB_descriptor_data.xlsx
+++ b/data/RouteB_descriptor_data.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,20 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -77,12 +91,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,16 +465,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Additional file 2 - Route B: descriptor data, correlation-based reduction and PLS-DA results.</t>
-        </is>
-      </c>
-    </row>
+          <t>Additional file 3 - Route B: descriptor data, correlation-based reduction and PLS-DA results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -479,23 +497,22 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>See the Descriptors, Computation_rules, Reduction, PLS-DA_reduced, VIP_reduced, VIP_two_stage,</t>
+          <t>See the Descriptors, Computation_rules, Pearson_Corr, Spearman_Corr, Reduction, PLS-DA_reduced, VIP_reduced,</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Comparison_3_routes, Conclusions and VIP_gt1_list sheets for the data and results themselves.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
+          <t>VIP_two_stage, Comparison_3_routes, Conclusions and VIP_gt1_list sheets for the data and results themselves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -548,7 +565,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>section of the manuscript and the NumStereoCenters column, which counts unassigned potential</t>
+          <t>section of the manuscript and the NumStereoCenters column, which counts assigned and unassigned CIP</t>
         </is>
       </c>
     </row>
@@ -563,6 +580,140 @@
       <c r="A19" t="inlineStr">
         <is>
           <t>"3-Carene, alpha-Carene" was modelled as 3-carene (car-3-ene), BQOFWKZOCNGFEC-UHFFFAOYSA-N.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>REVISION (03.10.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Software: RDKit 2026.03.6, Python 3.11.15. The RDKit version used for the submitted file was not recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>All 25 descriptor values were recomputed with this version from the input SMILES. Every submitted value was reproduced</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>except one: NumStereoCenters of 1,8-cineole, which the submitted file gave as 2. That file had used</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>FindMolChiralCenters(..., useLegacyImplementation=False), which also counts ring-bridgehead atoms as potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>stereo elements; the CIP-based count (useLegacyImplementation=True, the RDKit default) gives 0, the correct value for</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>this achiral molecule. The corrected value is used here and in the revised manuscript; the submitted values are kept</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>in column NumStereoCenters_submitted. Floating-point values are stored to six decimals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Pearson_Corr and Spearman_Corr were recomputed from the stored values. Spearman coefficients use average ranks for ties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>In the submitted file they had been computed from unrounded values, in which isomers of the same formula differ in MolWt</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>and LabuteASA in the 14th decimal; this broke ties and caused the deviations of up to 0.019 noted in review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Largest change of a Spearman coefficient against the submitted sheet: 0.2545 (NumStereoCenters / Ether_flag), including the effect of the</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>corrected stereocentre count. The 30 pairs with |r| or |rho| &gt; 0.7 (25 by both coefficients, 3 by Spearman only, 2 by</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Pearson only) and the reduction in the Reduction sheet are unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>NumStereoCenters is not among the 12 modelled descriptors, so PLS-DA_reduced and VIP_reduced are unchanged apart from</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>p-values, which now count ties as in Table 1. VIP_two_stage and VIP_gt1_list, which use all 25 descriptors, were</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>recomputed with the corrected value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>The summary sheets Comparison_3_routes and Conclusions were regenerated from the current results (the submitted versions</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>contained values of an earlier stage); every number in them is read from the same result files as Table 1 and Table 2.</t>
         </is>
       </c>
     </row>
@@ -577,43 +728,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Strain</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>(1) 2208 biased Q2</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>(2) 2208 nested Q2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>(3) 2208 nested p(Q2)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>(4) Literature-12 Q2 (nLV = 1, honest)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>(5) Literature-12 p(Q2)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Interpretation</t>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>(1) Route A2, apparent Q2 (selection on all compounds)</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>(2) Route A2, nested Q2 (selection inside every fold)</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>(3) Route A2, nested p(Q2)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>(4) Route B, 12 descriptors, Q2 (nLV = 1, honest)</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>(5) Route B, p(Q2)</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Reading</t>
         </is>
       </c>
     </row>
@@ -624,23 +775,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="C2" t="n">
         <v>-0.14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.15</v>
+        <v>0.1544</v>
       </c>
       <c r="E2" t="n">
-        <v>0.289</v>
+        <v>0.29</v>
       </c>
       <c r="F2" t="n">
         <v>0.002</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Literature set recovers an honest, significant signal</t>
+          <t>Route B: significant after Bonferroni correction (alpha = 0.0125); Route A2 nested: not significant</t>
         </is>
       </c>
     </row>
@@ -651,23 +802,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="C3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="D3" t="n">
         <v>0.013</v>
       </c>
       <c r="E3" t="n">
-        <v>0.394</v>
+        <v>0.39</v>
       </c>
       <c r="F3" t="n">
         <v>0.001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Literature set recovers an honest, significant signal</t>
+          <t>Route B: significant after Bonferroni correction (alpha = 0.0125); Route A2 nested: nominally significant (p &lt; 0.05)</t>
         </is>
       </c>
     </row>
@@ -678,23 +829,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="C4" t="n">
         <v>0.19</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01</v>
+        <v>0.0095</v>
       </c>
       <c r="E4" t="n">
-        <v>0.353</v>
+        <v>0.35</v>
       </c>
       <c r="F4" t="n">
         <v>0.0015</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Literature set recovers an honest, significant signal</t>
+          <t>Route B: significant after Bonferroni correction (alpha = 0.0125); Route A2 nested: significant after Bonferroni correction (alpha = 0.0125)</t>
         </is>
       </c>
     </row>
@@ -705,13 +856,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="C5" t="n">
         <v>-0.11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.13</v>
+        <v>0.1349</v>
       </c>
       <c r="E5" t="n">
         <v>0.05</v>
@@ -721,7 +872,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>weak / not significant under all routes</t>
+          <t>Route B: nominally significant (p &lt; 0.05); Route A2 nested: not significant</t>
         </is>
       </c>
     </row>
@@ -732,7 +883,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="C6" t="n">
         <v>0.4</v>
@@ -741,21 +892,50 @@
         <v>0.0015</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="F6" t="n">
         <v>0.0005</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Artefact (3 actives) - exclude</t>
-        </is>
-      </c>
-    </row>
+          <t>Artefact (3 actives): descriptive only, no p-value interpreted</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Despite its name, this sheet compares three CONDITIONS, not three of the manuscript's named routes (A1/A1u/A2/B): the 2208-descriptor pool used without nesting (biased, column 1), the same pool honestly nested (columns 2-3), and the small literature-derived 12-descriptor set (Route B; columns 4-5, honest by construction). Columns are numbered (1)-(5) in sequence; the literature set is labelled 'Literature-12', matching the 12-descriptor Route B set used throughout the manuscript.</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Regenerated for the revision from the result files behind Table 1 of the revised manuscript (Route A2 and Route B rows; apparent</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>values from the archived ordinary permutation runs). The sheet compares three conditions: the 2,208-descriptor pool of Route A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>with the selection made once on all compounds (column 1, optimistic), the same route with the selection repeated inside every</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>fold (columns 2 and 3, honest), and the 12 literature-derived descriptors of Route B (columns 4 and 5, honest by construction).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>p-values: 2,000 permutations, ties counted as in Table 1. The submitted version of this sheet contained values of an earlier stage.</t>
         </is>
       </c>
     </row>
@@ -770,275 +950,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CONCLUSIONS - literature-based descriptor selection (leakage-free)</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>CONCLUSIONS - literature-based descriptor selection (leakage-free); regenerated for the revision from the current results</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1) Key finding: with 12 literature-based descriptors (correlation-based reduction, one exactly redundant pair resolved), H. influenzae,</t>
-        </is>
-      </c>
+      <c r="A2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   S. aureus and S. pneumoniae show an HONESTLY significant, moderate signal (Q2 = 0.29-0.39, p &lt; 0.01)</t>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>1) Key finding: with the 12 literature-derived descriptors (correlation-based reduction, one exactly redundant pair resolved),</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - even at nLV = 1. These are exactly the endpoints that the 2,208-descriptor route lost almost</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   H. influenzae, S. aureus and S. pneumoniae show an honest, moderate signal already with one latent variable:</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   entirely (H.I., S.Pyo) or partly (S.A., S.Pneu) under nesting.</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Q2 = 0.29, 0.39 and 0.35, p = 0.0020, 0.0010 and 0.0015, all below the Bonferroni threshold of 0.0125 (Table 1).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2) Diagnostic value: the route SEPARATES the causes. The failure of the</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Under Route A2 (2,208 descriptors, selection inside every fold) the nested Q2 is −0.14 for H. influenzae (p = 0.1544, not significant),</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   2,208-descriptor pipeline was not (only) a missing signal, but overfitting/leakage of the supervised</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   0.15 for S. aureus (p = 0.0130) and 0.19 for S. pneumoniae (p = 0.0095); see sheet Comparison_3_routes.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   selection from too many candidates at n = 31. A small, theory-based, leakage-free set</t>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2) Diagnostic value: the failure of the 2,208-descriptor pipeline under nesting is not only a missing signal but the optimism of</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   makes the real (moderate) structure-activity signal visible.</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   supervised selection from many candidates at n = 31; a small, theory-based, leakage-free set makes the moderate signal visible.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>3) Why a SIMPLE permutation is honest here: the reduction uses only descriptor-descriptor</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>3) Why a simple permutation test is honest here: the reduction uses only descriptor-descriptor correlations (no activity labels),</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   correlation (no Y) -&gt; leakage-free. There is no supervised selection step to nest.</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   so there is no supervised selection step to nest.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   apparent ~ cross-validated (no large drop) - in contrast to the 2,208-descriptor route.</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>4) S. pyogenes remains weak with the 12 descriptors (Q2 = 0.05, p = 0.0360, nominal only; AUC p = 0.1219, not significant), despite the</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>4) S. pyogenes remains weak (Q2 = 0.05, n.s.) despite the largest active class (11) -&gt; endpoint-specific,</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   largest active class (11). With all 25 descriptors it reaches Q2 = 0.24 (p = 0.0040; Table 2): the reduction removed descriptors</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   not driven by the number of actives. Biologically interpretable.</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   that carry endpoint-specific information for this strain.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5) P. aeruginosa (3 actives) remains an overfitting artefact (AUC = 1.0) and is reported descriptively only.</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>5) P. aeruginosa (3 actives) is an overfitting artefact (AUC = 1.00) and is reported descriptively only.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>6) Multiplicity: under Bonferroni (alpha = 0.0125, four statistically evaluable endpoints) H.I. (0.0020), S.Pneu (0.0015) and S.A. pass (p(Q2)</t>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>6) Multiplicity: under Bonferroni (alpha = 0.0125, four evaluable endpoints) the Q2 of H. influenzae, S. aureus and S. pneumoniae</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   = 0.0010; p(AUC) = 0.0175, above the threshold).</t>
-        </is>
-      </c>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   passes; on AUC, S. aureus (p = 0.0175) does not, H. influenzae (p = 0.0015) and S. pneumoniae (p = 0.0075) do.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ON THE VIP QUESTION (PLS-DA with many descriptors, then keep only high VIP and refit):</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>ON THE VIP QUESTION (PLS-DA with many descriptors, then keep only VIP &gt; 1 and refit):</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>- As a selection method for the PERFORMANCE ESTIMATE this is legitimate only if the VIP selection is</t>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>- As a selection method for the performance estimate this is legitimate only if the VIP selection is repeated inside every</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  repeated INSIDE every CV fold (nested). Otherwise it is the same leakage trap as with the effect-size</t>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  cross-validation fold (nested); otherwise it is the same leakage as with the univariate filter, with VIP as the criterion.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  filter - only with VIP as the criterion.</t>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>- Sheet VIP_two_stage: the naive Q2 (selection on all data) exceeds the nested Q2 for every strain, e.g. H. influenzae 0.305 -&gt; 0.205,</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>- Evidence from sheet VIP_two_stage: naive VIP selection (on all data) &gt; nested VIP selection</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S. pneumoniae 0.513 -&gt; 0.246. That difference is the leakage.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  for Q2 throughout (e.g. H.I. 0.29 -&gt; 0.16; S.Pneu 0.53 -&gt; 0.31). That difference IS the</t>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>- Recommendation: use VIP for interpretation, not as a second selection step that flatters the reported performance.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  amount of leakage.</t>
-        </is>
-      </c>
+      <c r="A25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>- Recommendation: use VIP for INTERPRETATION (which descriptors contribute), not as a second selection</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>NOTE on the number of latent variables: nLV = 1 is the conservative baseline fixed a priori. The values in PLS-DA_reduced for the</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  to flatter the reported performance. With a good a priori set the second stage is usually</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>nLV that maximises Q2 on all compounds contain the optimism of that choice and are an upper bound; the selection-adjusted</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  unnecessary anyway - the reduced set already models honestly.</t>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>estimate is the doubly nested one in the Supplement (number of latent variables).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>ROBUSTNESS OF THE CORRELATION METRIC (Pearson vs. Spearman):</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>- Of the 30 pairs above 0.7, 25 are detected by both coefficients, 3 by Spearman only and 2 by Pearson only.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>NOTE on nLV: nLV = 1 is the conservative, honest baseline. The nLV-CV values (nLV 3-4) are higher but</t>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>- Decisive Spearman-only case: NumHDonors - TPSA (r = 0.57, rho = 0.72), monotonic but not linear.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>contain the optimism of choosing the component number by Q2; to be read as an upper bound.</t>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>- Pearson alone gives 14 representatives instead of 13 (before resolving the exactly redundant pair; afterwards 13 and 12):</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the representative of the size/polarity block shifts from TPSA to O_Count and NumHDonors becomes a singleton.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ROBUSTNESS OF THE CORRELATION METRIC (Pearson vs. Spearman):</t>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>- With the Pearson-only set the one-component LOO Q2 changes by at most 0.02 for the four evaluable endpoints, so the result is</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>- Of the pairs above 0.7, both metrics detected 25 jointly; 3 only Spearman, 2 only Pearson.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>- Decisive Spearman-only case: NumHDonors &lt;-&gt; TPSA (rP = 0.57, rS = 0.72) - monotonic but not</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  linear (discrete HBD count vs. continuous TPSA).</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>- Effect on the reduction is minimal: 14 representatives with Pearson alone vs. 13 combined (both counts are before</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  resolving the one exactly redundant pair; afterwards 13 and 12 respectively, matching the manuscript. Two</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  things change together in the size/polarity block: the representative shifts from TPSA to O_Count,</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  and NumHDonors splits off from that block as its own additional singleton. Model results are</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  practically unchanged -&gt; result robust to the choice of metric.</t>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  robust to the choice of metric.</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,11 +1238,11 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aldehyde_flag, FractionCSP3, Phenol_flag, CarboxAcid_flag, NumStereoCenters, NumAliphaticRings, NumHAcceptors, MolLogP</t>
+          <t>Aldehyde_flag, FractionCSP3, Phenol_flag, CarboxAcid_flag, NumAliphaticRings, NumHAcceptors, NumStereoCenters, MolLogP, TPSA</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1260,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Phenol_flag, NumAromaticRings, FractionCSP3, NumHDonors, DegreeUnsaturation, NumStereoCenters</t>
+          <t>Phenol_flag, NumAromaticRings, FractionCSP3, NumHDonors, DegreeUnsaturation, CeqC_DoubleBonds</t>
         </is>
       </c>
     </row>
@@ -1124,11 +1274,11 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Phenol_flag, FractionCSP3, NumAromaticRings, DegreeUnsaturation, NumStereoCenters, NumHAcceptors, CarboxAcid_flag, NumAliphaticRings</t>
+          <t>Phenol_flag, FractionCSP3, NumAromaticRings, DegreeUnsaturation, NumStereoCenters, NumHAcceptors, CarboxAcid_flag, NumAliphaticRings, TPSA</t>
         </is>
       </c>
     </row>
@@ -1165,6 +1315,14 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>NumHAcceptors, TPSA, HeavyAtomCount, MolWt, LabuteASA, O_Count, MolMR, Phenol_flag, NumAliphaticRings, NumHDonors</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Revision: recomputed with the corrected stereocentre count of 1,8-cineole (0 instead of 2).</t>
         </is>
       </c>
     </row>
@@ -1179,8 +1337,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI32"/>
+  <dimension ref="A1:AJ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="36" max="36"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1358,6 +1519,11 @@
           <t>LabuteASA</t>
         </is>
       </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>NumStereoCenters_submitted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1474,16 +1640,19 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.647700000000001</v>
+        <v>2.6477</v>
       </c>
       <c r="AG2" t="n">
         <v>17.07</v>
       </c>
       <c r="AH2" t="n">
-        <v>46.35000000000002</v>
+        <v>46.35</v>
       </c>
       <c r="AI2" t="n">
-        <v>69.17942100391355</v>
+        <v>69.179421</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1601,16 +1770,19 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.567800000000001</v>
+        <v>2.5678</v>
       </c>
       <c r="AG3" t="n">
         <v>17.07</v>
       </c>
       <c r="AH3" t="n">
-        <v>46.32600000000002</v>
+        <v>46.326</v>
       </c>
       <c r="AI3" t="n">
-        <v>68.48981797172929</v>
+        <v>68.489818</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1728,16 +1900,19 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.487900000000001</v>
+        <v>2.4879</v>
       </c>
       <c r="AG4" t="n">
         <v>17.07</v>
       </c>
       <c r="AH4" t="n">
-        <v>46.30200000000003</v>
+        <v>46.302</v>
       </c>
       <c r="AI4" t="n">
-        <v>67.80021493954504</v>
+        <v>67.80021499999999</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1819,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>3</v>
@@ -1855,16 +2030,19 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.744100000000001</v>
+        <v>2.7441</v>
       </c>
       <c r="AG5" t="n">
         <v>9.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>45.52700000000002</v>
+        <v>45.527</v>
       </c>
       <c r="AI5" t="n">
-        <v>69.12561297984743</v>
+        <v>69.125613</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1982,16 +2160,19 @@
         <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.831200000000002</v>
+        <v>2.8312</v>
       </c>
       <c r="AG6" t="n">
         <v>20.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>49.55580000000003</v>
+        <v>49.5558</v>
       </c>
       <c r="AI6" t="n">
-        <v>70.81796380959504</v>
+        <v>70.817964</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2109,16 +2290,19 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.998700000000001</v>
+        <v>2.9987</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>43.75200000000002</v>
+        <v>43.752</v>
       </c>
       <c r="AI7" t="n">
-        <v>63.3224647181563</v>
+        <v>63.322465</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2236,16 +2420,19 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.401700000000001</v>
+        <v>2.4017</v>
       </c>
       <c r="AG8" t="n">
         <v>17.07</v>
       </c>
       <c r="AH8" t="n">
-        <v>44.23600000000002</v>
+        <v>44.236</v>
       </c>
       <c r="AI8" t="n">
-        <v>68.17358985038432</v>
+        <v>68.17359</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2363,16 +2550,19 @@
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.824020000000001</v>
+        <v>2.82402</v>
       </c>
       <c r="AG9" t="n">
         <v>20.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>46.93280000000003</v>
+        <v>46.9328</v>
       </c>
       <c r="AI9" t="n">
-        <v>67.6854053292794</v>
+        <v>67.685405</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2496,10 +2686,13 @@
         <v>54.37</v>
       </c>
       <c r="AH10" t="n">
-        <v>48.31180000000002</v>
+        <v>48.3118</v>
       </c>
       <c r="AI10" t="n">
-        <v>78.13517685615334</v>
+        <v>78.135177</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2617,16 +2810,19 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.878000000000001</v>
+        <v>2.878</v>
       </c>
       <c r="AG11" t="n">
         <v>17.07</v>
       </c>
       <c r="AH11" t="n">
-        <v>48.48600000000003</v>
+        <v>48.486</v>
       </c>
       <c r="AI11" t="n">
-        <v>68.80604609307427</v>
+        <v>68.80604599999999</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2744,16 +2940,19 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.957900000000001</v>
+        <v>2.9579</v>
       </c>
       <c r="AG12" t="n">
         <v>17.07</v>
       </c>
       <c r="AH12" t="n">
-        <v>48.51000000000003</v>
+        <v>48.51</v>
       </c>
       <c r="AI12" t="n">
-        <v>69.49564912525854</v>
+        <v>69.495649</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2871,16 +3070,19 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.401700000000001</v>
+        <v>2.4017</v>
       </c>
       <c r="AG13" t="n">
         <v>17.07</v>
       </c>
       <c r="AH13" t="n">
-        <v>44.23600000000002</v>
+        <v>44.236</v>
       </c>
       <c r="AI13" t="n">
-        <v>68.17358985038432</v>
+        <v>68.17359</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -2998,16 +3200,19 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.763700000000001</v>
+        <v>2.7637</v>
       </c>
       <c r="AG14" t="n">
         <v>37.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>50.05780000000003</v>
+        <v>50.0578</v>
       </c>
       <c r="AI14" t="n">
-        <v>73.60027984527028</v>
+        <v>73.60028</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3083,7 +3288,7 @@
         <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7272729999999999</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -3125,16 +3330,19 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.828500000000001</v>
+        <v>2.8285</v>
       </c>
       <c r="AG15" t="n">
         <v>26.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>52.39600000000004</v>
+        <v>52.396</v>
       </c>
       <c r="AI15" t="n">
-        <v>79.96830531563279</v>
+        <v>79.968305</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3252,16 +3460,19 @@
         <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.669800000000001</v>
+        <v>2.6698</v>
       </c>
       <c r="AG16" t="n">
         <v>20.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>49.48580000000003</v>
+        <v>49.4858</v>
       </c>
       <c r="AI16" t="n">
-        <v>69.43875774522651</v>
+        <v>69.43875800000001</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -3379,16 +3590,19 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.118420000000002</v>
+        <v>3.11842</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>45.26800000000003</v>
+        <v>45.268</v>
       </c>
       <c r="AI17" t="n">
-        <v>62.89117157708339</v>
+        <v>62.891172</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3506,16 +3720,19 @@
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.439500000000001</v>
+        <v>2.4395</v>
       </c>
       <c r="AG18" t="n">
         <v>20.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>47.34980000000002</v>
+        <v>47.3498</v>
       </c>
       <c r="AI18" t="n">
-        <v>69.8121326560658</v>
+        <v>69.812133</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3633,16 +3850,19 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.475000000000002</v>
+        <v>3.475</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>48.00200000000003</v>
+        <v>48.002</v>
       </c>
       <c r="AI19" t="n">
-        <v>63.95492096084624</v>
+        <v>63.954921</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3760,16 +3980,19 @@
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.118420000000002</v>
+        <v>3.11842</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>45.26800000000003</v>
+        <v>45.268</v>
       </c>
       <c r="AI20" t="n">
-        <v>62.89117157708339</v>
+        <v>62.891172</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3887,16 +4110,19 @@
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.767700000000001</v>
+        <v>2.7677</v>
       </c>
       <c r="AG21" t="n">
         <v>9.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>47.56900000000002</v>
+        <v>47.569</v>
       </c>
       <c r="AI21" t="n">
-        <v>69.44184110119241</v>
+        <v>69.441841</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -4014,16 +4240,19 @@
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.193500000000001</v>
+        <v>2.1935</v>
       </c>
       <c r="AG22" t="n">
         <v>20.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>45.23580000000002</v>
+        <v>45.2358</v>
       </c>
       <c r="AI22" t="n">
-        <v>68.80630150253657</v>
+        <v>68.806302</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -4141,16 +4370,19 @@
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.487900000000001</v>
+        <v>2.4879</v>
       </c>
       <c r="AG23" t="n">
         <v>17.07</v>
       </c>
       <c r="AH23" t="n">
-        <v>46.30200000000003</v>
+        <v>46.302</v>
       </c>
       <c r="AI23" t="n">
-        <v>67.80021493954504</v>
+        <v>67.80021499999999</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4268,16 +4500,19 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.453000000000002</v>
+        <v>3.453</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>45.98200000000003</v>
+        <v>45.982</v>
       </c>
       <c r="AI24" t="n">
-        <v>63.63869283950128</v>
+        <v>63.638693</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -4395,16 +4630,19 @@
         <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.973700000000002</v>
+        <v>2.9737</v>
       </c>
       <c r="AG25" t="n">
         <v>20.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>49.60380000000003</v>
+        <v>49.6038</v>
       </c>
       <c r="AI25" t="n">
-        <v>70.81796380959503</v>
+        <v>70.817964</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -4522,16 +4760,19 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.824020000000001</v>
+        <v>2.82402</v>
       </c>
       <c r="AG26" t="n">
         <v>20.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>46.93280000000003</v>
+        <v>46.9328</v>
       </c>
       <c r="AI26" t="n">
-        <v>67.6854053292794</v>
+        <v>67.685405</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -4655,10 +4896,13 @@
         <v>34.14</v>
       </c>
       <c r="AH27" t="n">
-        <v>46.69200000000002</v>
+        <v>46.692</v>
       </c>
       <c r="AI27" t="n">
-        <v>71.9617370395888</v>
+        <v>71.961737</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4782,10 +5026,13 @@
         <v>17.07</v>
       </c>
       <c r="AH28" t="n">
-        <v>44.16600000000002</v>
+        <v>44.166</v>
       </c>
       <c r="AI28" t="n">
-        <v>68.17358985038432</v>
+        <v>68.17359</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -4903,16 +5150,19 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>3.164800000000002</v>
+        <v>3.1648</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>45.84200000000003</v>
+        <v>45.842</v>
       </c>
       <c r="AI29" t="n">
-        <v>63.63869283950127</v>
+        <v>63.638693</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -5030,16 +5280,19 @@
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.998700000000001</v>
+        <v>2.9987</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>43.75200000000002</v>
+        <v>43.752</v>
       </c>
       <c r="AI30" t="n">
-        <v>63.3224647181563</v>
+        <v>63.322465</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -5157,16 +5410,19 @@
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.711900000000001</v>
+        <v>2.7119</v>
       </c>
       <c r="AG31" t="n">
         <v>17.07</v>
       </c>
       <c r="AH31" t="n">
-        <v>46.39600000000003</v>
+        <v>46.396</v>
       </c>
       <c r="AI31" t="n">
-        <v>68.48981797172931</v>
+        <v>68.489818</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -5290,10 +5546,13 @@
         <v>37.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>48.46580000000003</v>
+        <v>48.4658</v>
       </c>
       <c r="AI32" t="n">
-        <v>71.49247287485878</v>
+        <v>71.492473</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5553,12 +5812,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FindMolChiralCenters(includeUnassigned=True)</t>
+          <t>FindMolChiralCenters(includeUnassigned=True, useLegacyImplementation=True)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Assigned and potential stereocentres</t>
+          <t>Assigned and unassigned CIP stereocentres; ring-bridgehead atoms that are not stereogenic are not counted (1,8-cineole = 0). The submitted version used useLegacyImplementation=False (1,8-cineole = 2); those values are kept in column NumStereoCenters_submitted of the Descriptors sheet.</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6427,7 @@
         <v>-0.1834</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1344</v>
+        <v>0.1244</v>
       </c>
       <c r="L2" t="n">
         <v>-0.08790000000000001</v>
@@ -6250,7 +6509,7 @@
         <v>0.032</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0172</v>
+        <v>-0.0057</v>
       </c>
       <c r="L3" t="n">
         <v>0.0198</v>
@@ -6332,7 +6591,7 @@
         <v>-0.1597</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0496</v>
+        <v>0.0465</v>
       </c>
       <c r="L4" t="n">
         <v>-0.109</v>
@@ -6414,7 +6673,7 @@
         <v>-0.1382</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0412</v>
+        <v>0.0411</v>
       </c>
       <c r="L5" t="n">
         <v>-0.0948</v>
@@ -6496,7 +6755,7 @@
         <v>-0.3804</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5415</v>
+        <v>0.3882</v>
       </c>
       <c r="L6" t="n">
         <v>0.9113</v>
@@ -6578,7 +6837,7 @@
         <v>-0.4001</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4682</v>
+        <v>-0.439</v>
       </c>
       <c r="L7" t="n">
         <v>-0.4437</v>
@@ -6660,7 +6919,7 @@
         <v>0.2237</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2435</v>
+        <v>-0.1773</v>
       </c>
       <c r="L8" t="n">
         <v>-0.6176</v>
@@ -6742,7 +7001,7 @@
         <v>-0.4569</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8277</v>
+        <v>0.7347</v>
       </c>
       <c r="L9" t="n">
         <v>0.5765</v>
@@ -6824,7 +7083,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4276</v>
+        <v>-0.3688</v>
       </c>
       <c r="L10" t="n">
         <v>-0.1762</v>
@@ -6879,79 +7138,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1344</v>
+        <v>0.1244</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0172</v>
+        <v>-0.0057</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0496</v>
+        <v>0.0465</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0412</v>
+        <v>0.0411</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5415</v>
+        <v>0.3882</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4682</v>
+        <v>-0.439</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2435</v>
+        <v>-0.1773</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8277</v>
+        <v>0.7347</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4276</v>
+        <v>-0.3688</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6785</v>
+        <v>0.5289</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4781</v>
+        <v>-0.4292</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0022</v>
+        <v>0.0453</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0689</v>
+        <v>0.0584</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2975</v>
+        <v>-0.2689</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3998</v>
+        <v>0.432</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.0247</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3495</v>
+        <v>-0.3276</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2309</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0172</v>
+        <v>-0.0057</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3002</v>
+        <v>0.3265</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3103</v>
+        <v>-0.3177</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0137</v>
+        <v>0.0515</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.3383</v>
+        <v>-0.2952</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1141</v>
+        <v>0.1055</v>
       </c>
     </row>
     <row r="12">
@@ -6988,7 +7247,7 @@
         <v>-0.1762</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6785</v>
+        <v>0.5289</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -7070,7 +7329,7 @@
         <v>0.2231</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4781</v>
+        <v>-0.4292</v>
       </c>
       <c r="L13" t="n">
         <v>-0.0433</v>
@@ -7152,7 +7411,7 @@
         <v>-0.3293</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0022</v>
+        <v>0.0453</v>
       </c>
       <c r="L14" t="n">
         <v>-0.389</v>
@@ -7234,7 +7493,7 @@
         <v>-0.208</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0689</v>
+        <v>0.0584</v>
       </c>
       <c r="L15" t="n">
         <v>-0.0793</v>
@@ -7316,7 +7575,7 @@
         <v>0.3632</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2975</v>
+        <v>-0.2689</v>
       </c>
       <c r="L16" t="n">
         <v>-0.1489</v>
@@ -7398,7 +7657,7 @@
         <v>-0.241</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3998</v>
+        <v>0.432</v>
       </c>
       <c r="L17" t="n">
         <v>0.3178</v>
@@ -7480,7 +7739,7 @@
         <v>0.0461</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0247</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="L18" t="n">
         <v>-0.1186</v>
@@ -7562,7 +7821,7 @@
         <v>-0.2987</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3495</v>
+        <v>-0.3276</v>
       </c>
       <c r="L19" t="n">
         <v>-0.3312</v>
@@ -7644,7 +7903,7 @@
         <v>-0.0968</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2309</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="L20" t="n">
         <v>0.3226</v>
@@ -7726,7 +7985,7 @@
         <v>0.032</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0172</v>
+        <v>-0.0057</v>
       </c>
       <c r="L21" t="n">
         <v>0.0198</v>
@@ -7808,7 +8067,7 @@
         <v>-0.2093</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3002</v>
+        <v>0.3265</v>
       </c>
       <c r="L22" t="n">
         <v>-0.1489</v>
@@ -7890,7 +8149,7 @@
         <v>0.2937</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3103</v>
+        <v>-0.3177</v>
       </c>
       <c r="L23" t="n">
         <v>-0.2122</v>
@@ -7972,7 +8231,7 @@
         <v>-0.1796</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0137</v>
+        <v>0.0515</v>
       </c>
       <c r="L24" t="n">
         <v>-0.2019</v>
@@ -8054,7 +8313,7 @@
         <v>0.2095</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3383</v>
+        <v>-0.2952</v>
       </c>
       <c r="L25" t="n">
         <v>-0.6363</v>
@@ -8136,7 +8395,7 @@
         <v>-0.1453</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1141</v>
+        <v>0.1055</v>
       </c>
       <c r="L26" t="n">
         <v>-0.1126</v>
@@ -8335,76 +8594,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2872</v>
+        <v>0.2888</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8742</v>
+        <v>0.8792</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8748</v>
+        <v>0.8797</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2389</v>
+        <v>-0.2508</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3104</v>
+        <v>-0.3022</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4353</v>
+        <v>0.4442</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3532</v>
+        <v>0.3504</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1741</v>
+        <v>-0.1819</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2173</v>
+        <v>0.1954</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0523</v>
+        <v>-0.0641</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3819</v>
+        <v>-0.384</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4845</v>
+        <v>0.4873</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8403</v>
+        <v>0.8451</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1035</v>
+        <v>-0.114</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1994</v>
+        <v>0.2179</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4131</v>
+        <v>0.4154</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0306</v>
+        <v>-0.0185</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1475</v>
+        <v>0.1335</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2872</v>
+        <v>0.2888</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3646</v>
+        <v>0.3567</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.5627</v>
+        <v>-0.5612</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8186</v>
+        <v>0.8258</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6367</v>
+        <v>0.6454</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9903</v>
       </c>
     </row>
     <row r="3">
@@ -8414,7 +8673,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2872</v>
+        <v>0.2888</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -8441,7 +8700,7 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.0215</v>
       </c>
       <c r="L3" t="n">
         <v>0.0544</v>
@@ -8486,7 +8745,7 @@
         <v>0.3063</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3064</v>
+        <v>0.3065</v>
       </c>
     </row>
     <row r="4">
@@ -8496,7 +8755,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8742</v>
+        <v>0.8792</v>
       </c>
       <c r="C4" t="n">
         <v>0.2933</v>
@@ -8523,7 +8782,7 @@
         <v>-0.133</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0342</v>
+        <v>0.0264</v>
       </c>
       <c r="L4" t="n">
         <v>-0.0751</v>
@@ -8568,7 +8827,7 @@
         <v>0.5555</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.8698</v>
       </c>
     </row>
     <row r="5">
@@ -8578,7 +8837,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8748</v>
+        <v>0.8797</v>
       </c>
       <c r="C5" t="n">
         <v>0.34</v>
@@ -8605,7 +8864,7 @@
         <v>-0.1312</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0392</v>
+        <v>0.0319</v>
       </c>
       <c r="L5" t="n">
         <v>-0.06909999999999999</v>
@@ -8650,7 +8909,7 @@
         <v>0.5621</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8713</v>
+        <v>0.8715000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -8660,7 +8919,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2389</v>
+        <v>-0.2508</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -8687,7 +8946,7 @@
         <v>-0.3813</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5361</v>
+        <v>0.4029</v>
       </c>
       <c r="L6" t="n">
         <v>0.8653999999999999</v>
@@ -8732,7 +8991,7 @@
         <v>-0.8364</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.3495</v>
+        <v>-0.3496</v>
       </c>
     </row>
     <row r="7">
@@ -8742,7 +9001,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3104</v>
+        <v>-0.3022</v>
       </c>
       <c r="C7" t="n">
         <v>-0.0801</v>
@@ -8769,7 +9028,7 @@
         <v>-0.4232</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4893</v>
+        <v>-0.4658</v>
       </c>
       <c r="L7" t="n">
         <v>-0.4964</v>
@@ -8814,7 +9073,7 @@
         <v>-0.0392</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.3239</v>
+        <v>-0.324</v>
       </c>
     </row>
     <row r="8">
@@ -8824,7 +9083,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4353</v>
+        <v>0.4442</v>
       </c>
       <c r="C8" t="n">
         <v>0.2181</v>
@@ -8851,7 +9110,7 @@
         <v>0.2191</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2672</v>
+        <v>-0.1526</v>
       </c>
       <c r="L8" t="n">
         <v>-0.6965</v>
@@ -8896,7 +9155,7 @@
         <v>0.8309</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.517</v>
+        <v>0.5191</v>
       </c>
     </row>
     <row r="9">
@@ -8906,7 +9165,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3532</v>
+        <v>0.3504</v>
       </c>
       <c r="C9" t="n">
         <v>0.0412</v>
@@ -8933,7 +9192,7 @@
         <v>-0.4191</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8325</v>
+        <v>0.7346</v>
       </c>
       <c r="L9" t="n">
         <v>0.575</v>
@@ -8978,7 +9237,7 @@
         <v>-0.1513</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.2917</v>
+        <v>0.2918</v>
       </c>
     </row>
     <row r="10">
@@ -8988,7 +9247,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1741</v>
+        <v>-0.1819</v>
       </c>
       <c r="C10" t="n">
         <v>0.06610000000000001</v>
@@ -9015,7 +9274,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3884</v>
+        <v>-0.3155</v>
       </c>
       <c r="L10" t="n">
         <v>-0.106</v>
@@ -9070,79 +9329,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2173</v>
+        <v>0.1954</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.0215</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0342</v>
+        <v>0.0264</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0392</v>
+        <v>0.0319</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5361</v>
+        <v>0.4029</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4893</v>
+        <v>-0.4658</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2672</v>
+        <v>-0.1526</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8325</v>
+        <v>0.7346</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3884</v>
+        <v>-0.3155</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.698</v>
+        <v>0.5737</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.587</v>
+        <v>-0.5182</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0162</v>
+        <v>0.0285</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0825</v>
+        <v>0.0708</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2936</v>
+        <v>-0.2588</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4033</v>
+        <v>0.4325</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.0231</v>
+        <v>-0.0077</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3652</v>
+        <v>-0.3477</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2468</v>
+        <v>-0.0077</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.0215</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2884</v>
+        <v>0.3209</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3686</v>
+        <v>-0.3505</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.0304</v>
+        <v>0.0279</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.3527</v>
+        <v>-0.2872</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1515</v>
+        <v>0.1405</v>
       </c>
     </row>
     <row r="12">
@@ -9152,7 +9411,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.0523</v>
+        <v>-0.0641</v>
       </c>
       <c r="C12" t="n">
         <v>0.0544</v>
@@ -9179,7 +9438,7 @@
         <v>-0.106</v>
       </c>
       <c r="K12" t="n">
-        <v>0.698</v>
+        <v>0.5737</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -9234,7 +9493,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.3819</v>
+        <v>-0.384</v>
       </c>
       <c r="C13" t="n">
         <v>0.0108</v>
@@ -9261,7 +9520,7 @@
         <v>0.1602</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.587</v>
+        <v>-0.5182</v>
       </c>
       <c r="L13" t="n">
         <v>-0.1326</v>
@@ -9306,7 +9565,7 @@
         <v>-0.2445</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.3803</v>
+        <v>-0.3805</v>
       </c>
     </row>
     <row r="14">
@@ -9316,7 +9575,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4845</v>
+        <v>0.4873</v>
       </c>
       <c r="C14" t="n">
         <v>-0.126</v>
@@ -9343,7 +9602,7 @@
         <v>-0.358</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0162</v>
+        <v>0.0285</v>
       </c>
       <c r="L14" t="n">
         <v>-0.4152</v>
@@ -9388,7 +9647,7 @@
         <v>0.494</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.4401</v>
+        <v>0.4403</v>
       </c>
     </row>
     <row r="15">
@@ -9398,7 +9657,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8403</v>
+        <v>0.8451</v>
       </c>
       <c r="C15" t="n">
         <v>0.3251</v>
@@ -9425,7 +9684,7 @@
         <v>-0.1956</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0825</v>
+        <v>0.0708</v>
       </c>
       <c r="L15" t="n">
         <v>-0.0259</v>
@@ -9470,7 +9729,7 @@
         <v>0.5047</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.8369</v>
+        <v>0.8372000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -9480,7 +9739,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1035</v>
+        <v>-0.114</v>
       </c>
       <c r="C16" t="n">
         <v>-0.0801</v>
@@ -9507,7 +9766,7 @@
         <v>0.3968</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2936</v>
+        <v>-0.2588</v>
       </c>
       <c r="L16" t="n">
         <v>-0.1202</v>
@@ -9552,7 +9811,7 @@
         <v>0.1177</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.0294</v>
+        <v>-0.0344</v>
       </c>
     </row>
     <row r="17">
@@ -9562,7 +9821,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1994</v>
+        <v>0.2179</v>
       </c>
       <c r="C17" t="n">
         <v>-0.09859999999999999</v>
@@ -9589,7 +9848,7 @@
         <v>-0.2467</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4033</v>
+        <v>0.4325</v>
       </c>
       <c r="L17" t="n">
         <v>0.3953</v>
@@ -9634,7 +9893,7 @@
         <v>-0.2675</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1727</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="18">
@@ -9644,7 +9903,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4131</v>
+        <v>0.4154</v>
       </c>
       <c r="C18" t="n">
         <v>-0.0479</v>
@@ -9671,7 +9930,7 @@
         <v>0.0396</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0231</v>
+        <v>-0.0077</v>
       </c>
       <c r="L18" t="n">
         <v>-0.1095</v>
@@ -9716,7 +9975,7 @@
         <v>0.3084</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.3967</v>
+        <v>0.3968</v>
       </c>
     </row>
     <row r="19">
@@ -9726,7 +9985,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.0306</v>
+        <v>-0.0185</v>
       </c>
       <c r="C19" t="n">
         <v>-0.0598</v>
@@ -9753,7 +10012,7 @@
         <v>-0.3159</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3652</v>
+        <v>-0.3477</v>
       </c>
       <c r="L19" t="n">
         <v>-0.3705</v>
@@ -9808,7 +10067,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1475</v>
+        <v>0.1335</v>
       </c>
       <c r="C20" t="n">
         <v>-0.0479</v>
@@ -9835,7 +10094,7 @@
         <v>-0.07920000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2468</v>
+        <v>-0.0077</v>
       </c>
       <c r="L20" t="n">
         <v>0.266</v>
@@ -9880,7 +10139,7 @@
         <v>-0.0294</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.1322</v>
+        <v>0.1323</v>
       </c>
     </row>
     <row r="21">
@@ -9890,7 +10149,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2872</v>
+        <v>0.2888</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -9917,7 +10176,7 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.0215</v>
       </c>
       <c r="L21" t="n">
         <v>0.0544</v>
@@ -9962,7 +10221,7 @@
         <v>0.3063</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.3064</v>
+        <v>0.3065</v>
       </c>
     </row>
     <row r="22">
@@ -9972,7 +10231,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3646</v>
+        <v>0.3567</v>
       </c>
       <c r="C22" t="n">
         <v>-0.0801</v>
@@ -9999,7 +10258,7 @@
         <v>-0.2275</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2884</v>
+        <v>0.3209</v>
       </c>
       <c r="L22" t="n">
         <v>-0.1568</v>
@@ -10044,7 +10303,7 @@
         <v>0.2943</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.3337</v>
+        <v>0.3338</v>
       </c>
     </row>
     <row r="23">
@@ -10054,7 +10313,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5627</v>
+        <v>-0.5612</v>
       </c>
       <c r="C23" t="n">
         <v>0.08169999999999999</v>
@@ -10081,7 +10340,7 @@
         <v>0.2812</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3686</v>
+        <v>-0.3505</v>
       </c>
       <c r="L23" t="n">
         <v>-0.3484</v>
@@ -10126,7 +10385,7 @@
         <v>0.0414</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.5079</v>
+        <v>-0.5083</v>
       </c>
     </row>
     <row r="24">
@@ -10136,7 +10395,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8186</v>
+        <v>0.8258</v>
       </c>
       <c r="C24" t="n">
         <v>0.2311</v>
@@ -10163,7 +10422,7 @@
         <v>-0.2136</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0304</v>
+        <v>0.0279</v>
       </c>
       <c r="L24" t="n">
         <v>-0.2613</v>
@@ -10208,7 +10467,7 @@
         <v>0.6194</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.8017</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="25">
@@ -10218,7 +10477,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6367</v>
+        <v>0.6454</v>
       </c>
       <c r="C25" t="n">
         <v>0.3063</v>
@@ -10245,7 +10504,7 @@
         <v>0.1922</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3527</v>
+        <v>-0.2872</v>
       </c>
       <c r="L25" t="n">
         <v>-0.6983</v>
@@ -10290,7 +10549,7 @@
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.7167</v>
+        <v>0.7165</v>
       </c>
     </row>
     <row r="26">
@@ -10300,76 +10559,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9903</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3064</v>
+        <v>0.3065</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.8698</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8713</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3495</v>
+        <v>-0.3496</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3239</v>
+        <v>-0.324</v>
       </c>
       <c r="H26" t="n">
-        <v>0.517</v>
+        <v>0.5191</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2917</v>
+        <v>0.2918</v>
       </c>
       <c r="J26" t="n">
         <v>-0.0886</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1515</v>
+        <v>0.1405</v>
       </c>
       <c r="L26" t="n">
         <v>-0.1358</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3803</v>
+        <v>-0.3805</v>
       </c>
       <c r="N26" t="n">
-        <v>0.4401</v>
+        <v>0.4403</v>
       </c>
       <c r="O26" t="n">
-        <v>0.8369</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.0294</v>
+        <v>-0.0344</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1727</v>
+        <v>0.177</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3967</v>
+        <v>0.3968</v>
       </c>
       <c r="S26" t="n">
         <v>-0.0488</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1322</v>
+        <v>0.1323</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3064</v>
+        <v>0.3065</v>
       </c>
       <c r="V26" t="n">
-        <v>0.3337</v>
+        <v>0.3338</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.5079</v>
+        <v>-0.5083</v>
       </c>
       <c r="X26" t="n">
-        <v>0.8017</v>
+        <v>0.802</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.7167</v>
+        <v>0.7165</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
@@ -10621,17 +10880,18 @@
         <v>1</v>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Note. The correlation grouping above retains 13 representatives (25 descriptors total, matching Table</t>
+          <t>Note. The correlation grouping above retains 13 representatives (25 descriptors total, matching</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S4). Among them one pair is exactly redundant: C_Count and EsterLacton_flag have r = rho = 1.000,</t>
+          <t>Table S7). Among them one pair is exactly redundant: C_Count and EsterLacton_flag have r = rho = 1.000,</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10841,7 +11101,7 @@
         <v>0.0015</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0065</v>
+        <v>0.0075</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
@@ -10927,6 +11187,14 @@
       <c r="J6" t="inlineStr">
         <is>
           <t>3/0/0/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>p-values count permuted values within 1e-9 of the observed value as ties, as in Table 1 of the manuscript.</t>
         </is>
       </c>
     </row>
@@ -11284,10 +11552,11 @@
         <v>0.168</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>nLV = 2 for every strain (apparent VIP, matching Fig. S2b/Fig. S3a and Additional file 5's convention); the footnote below gives its own source rather than pointing to VIP_gt1_list (25-descriptor set). C_Count is not listed: it is exactly redundant with EsterLacton_flag (r = rho = 1.000, see the Reduction sheet) and is excluded from the 12-descriptor modelling set, so it has no VIP in this set. Source: figures/data_recalc/vip_routeB.json, key D12, field 'apparent'.</t>
+          <t>nLV = 2 for every strain (apparent VIP, matching Fig. S3b/Fig. S4a and Additional file 8's convention); the footnote below gives its own source rather than pointing to VIP_gt1_list (25-descriptor set). C_Count is not listed: it is exactly redundant with EsterLacton_flag (r = rho = 1.000, see the Reduction sheet) and is excluded from the 12-descriptor modelling set, so it has no VIP in this set. Source: figures/data_recalc/vip_routeB.json, key D12, field 'apparent'.</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11360,19 +11629,19 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.287</v>
+        <v>0.305</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.871</v>
       </c>
       <c r="F2" t="n">
-        <v>0.161</v>
+        <v>0.205</v>
       </c>
       <c r="G2" t="n">
-        <v>0.805</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -11416,19 +11685,19 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.498</v>
+        <v>0.495</v>
       </c>
       <c r="E4" t="n">
         <v>0.931</v>
       </c>
       <c r="F4" t="n">
-        <v>0.424</v>
+        <v>0.436</v>
       </c>
       <c r="G4" t="n">
-        <v>0.877</v>
+        <v>0.885</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -11444,16 +11713,16 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.525</v>
+        <v>0.513</v>
       </c>
       <c r="E5" t="n">
         <v>0.96</v>
       </c>
       <c r="F5" t="n">
-        <v>0.305</v>
+        <v>0.246</v>
       </c>
       <c r="G5" t="n">
-        <v>0.853</v>
+        <v>0.847</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -11485,6 +11754,28 @@
       </c>
       <c r="H6" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Revision: recomputed with the corrected stereocentre count of 1,8-cineole (0 instead of 2); algorithm and nLV unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Submitted values (Q2 naive / nested): H.I. 0.287 / 0.161; S.A. 0.498 / 0.424; S.Pneu 0.525 / 0.305; S.Pyo 0.318 / 0.245; P.A. 0.998 / 0.995.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>The naive Q2 remains higher than the nested Q2 for every strain.</t>
+        </is>
       </c>
     </row>
   </sheetData>
